--- a/data/single_run/input/components/units/units_meisner.xlsx
+++ b/data/single_run/input/components/units/units_meisner.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K43"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1039,28 +1039,36 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>r1_10</t>
+          <t>r2_1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>DCR</t>
+          <t>DCS</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>2</v>
       </c>
-      <c r="E20" t="n">
-        <v>27</v>
-      </c>
-      <c r="F20" t="n">
-        <v>28</v>
-      </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>normal_by_triage</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="I20" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>180</v>
+      </c>
+      <c r="K20" t="n">
+        <v>83</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1070,28 +1078,36 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>r1_10</t>
+          <t>r2_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>PEC</t>
+          <t>DCS</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>2</v>
       </c>
-      <c r="E21" t="n">
-        <v>27</v>
-      </c>
-      <c r="F21" t="n">
-        <v>28</v>
-      </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>normal_by_triage</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="I21" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>180</v>
+      </c>
+      <c r="K21" t="n">
+        <v>83</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1101,28 +1117,36 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>r1_11</t>
+          <t>r2_3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>DCR</t>
+          <t>DCS</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>2</v>
       </c>
-      <c r="E22" t="n">
-        <v>27</v>
-      </c>
-      <c r="F22" t="n">
-        <v>28</v>
-      </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>normal_by_triage</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="I22" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>180</v>
+      </c>
+      <c r="K22" t="n">
+        <v>83</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1132,28 +1156,36 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>r1_11</t>
+          <t>r2_4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>PEC</t>
+          <t>DCS</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>2</v>
       </c>
-      <c r="E23" t="n">
-        <v>27</v>
-      </c>
-      <c r="F23" t="n">
-        <v>28</v>
-      </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>normal_by_triage</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="I23" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="J23" t="n">
+        <v>180</v>
+      </c>
+      <c r="K23" t="n">
+        <v>83</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1163,28 +1195,36 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>r1_12</t>
+          <t>r2_5</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>DCR</t>
+          <t>DCS</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>2</v>
       </c>
-      <c r="E24" t="n">
-        <v>27</v>
-      </c>
-      <c r="F24" t="n">
-        <v>28</v>
-      </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>normal_by_triage</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="I24" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="J24" t="n">
+        <v>180</v>
+      </c>
+      <c r="K24" t="n">
+        <v>83</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1194,28 +1234,36 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>r1_12</t>
+          <t>r2_6</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>PEC</t>
+          <t>DCS</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>2</v>
       </c>
-      <c r="E25" t="n">
-        <v>27</v>
-      </c>
-      <c r="F25" t="n">
-        <v>28</v>
-      </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>normal_by_triage</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="I25" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="J25" t="n">
+        <v>180</v>
+      </c>
+      <c r="K25" t="n">
+        <v>83</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1225,28 +1273,36 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>r1_13</t>
+          <t>r2_7</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>DCR</t>
+          <t>DCS</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>2</v>
       </c>
-      <c r="E26" t="n">
-        <v>27</v>
-      </c>
-      <c r="F26" t="n">
-        <v>28</v>
-      </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>normal_by_triage</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="I26" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="J26" t="n">
+        <v>180</v>
+      </c>
+      <c r="K26" t="n">
+        <v>83</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1256,28 +1312,36 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>r1_13</t>
+          <t>r2_8</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>PEC</t>
+          <t>DCS</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>2</v>
       </c>
-      <c r="E27" t="n">
-        <v>27</v>
-      </c>
-      <c r="F27" t="n">
-        <v>28</v>
-      </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>normal_by_triage</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>93.90000000000001</v>
+      </c>
+      <c r="I27" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="J27" t="n">
+        <v>180</v>
+      </c>
+      <c r="K27" t="n">
+        <v>83</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1287,587 +1351,34 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>r1_14</t>
+          <t>r2_9</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>DCR</t>
+          <t>DCS</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>2</v>
       </c>
-      <c r="E28" t="n">
-        <v>27</v>
-      </c>
-      <c r="F28" t="n">
-        <v>28</v>
-      </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>U028</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>r1_14</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>PEC</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>2</v>
-      </c>
-      <c r="E29" t="n">
-        <v>27</v>
-      </c>
-      <c r="F29" t="n">
-        <v>28</v>
-      </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>U029</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>r1_15</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>DCR</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>2</v>
-      </c>
-      <c r="E30" t="n">
-        <v>27</v>
-      </c>
-      <c r="F30" t="n">
-        <v>28</v>
-      </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>U030</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>r1_15</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>PEC</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>2</v>
-      </c>
-      <c r="E31" t="n">
-        <v>27</v>
-      </c>
-      <c r="F31" t="n">
-        <v>28</v>
-      </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>U031</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>r2_1</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>DCS</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>2</v>
-      </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr">
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
         <is>
           <t>normal_by_triage</t>
         </is>
       </c>
-      <c r="H32" t="n">
+      <c r="H28" t="n">
         <v>93.90000000000001</v>
       </c>
-      <c r="I32" t="n">
+      <c r="I28" t="n">
         <v>41.3</v>
       </c>
-      <c r="J32" t="n">
+      <c r="J28" t="n">
         <v>180</v>
       </c>
-      <c r="K32" t="n">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>U032</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>r2_2</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>DCS</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>2</v>
-      </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>normal_by_triage</t>
-        </is>
-      </c>
-      <c r="H33" t="n">
-        <v>93.90000000000001</v>
-      </c>
-      <c r="I33" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="J33" t="n">
-        <v>180</v>
-      </c>
-      <c r="K33" t="n">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>U033</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>r2_3</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>DCS</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>2</v>
-      </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>normal_by_triage</t>
-        </is>
-      </c>
-      <c r="H34" t="n">
-        <v>93.90000000000001</v>
-      </c>
-      <c r="I34" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="J34" t="n">
-        <v>180</v>
-      </c>
-      <c r="K34" t="n">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>U034</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>r2_4</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>DCS</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>2</v>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>normal_by_triage</t>
-        </is>
-      </c>
-      <c r="H35" t="n">
-        <v>93.90000000000001</v>
-      </c>
-      <c r="I35" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="J35" t="n">
-        <v>180</v>
-      </c>
-      <c r="K35" t="n">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>U035</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>r2_5</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>DCS</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>2</v>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>normal_by_triage</t>
-        </is>
-      </c>
-      <c r="H36" t="n">
-        <v>93.90000000000001</v>
-      </c>
-      <c r="I36" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="J36" t="n">
-        <v>180</v>
-      </c>
-      <c r="K36" t="n">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>U036</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>r2_6</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>DCS</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>2</v>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>normal_by_triage</t>
-        </is>
-      </c>
-      <c r="H37" t="n">
-        <v>93.90000000000001</v>
-      </c>
-      <c r="I37" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="J37" t="n">
-        <v>180</v>
-      </c>
-      <c r="K37" t="n">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>U037</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>r2_7</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>DCS</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>2</v>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>normal_by_triage</t>
-        </is>
-      </c>
-      <c r="H38" t="n">
-        <v>93.90000000000001</v>
-      </c>
-      <c r="I38" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="J38" t="n">
-        <v>180</v>
-      </c>
-      <c r="K38" t="n">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>U038</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>r2_8</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>DCS</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>2</v>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>normal_by_triage</t>
-        </is>
-      </c>
-      <c r="H39" t="n">
-        <v>93.90000000000001</v>
-      </c>
-      <c r="I39" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="J39" t="n">
-        <v>180</v>
-      </c>
-      <c r="K39" t="n">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>U039</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>r2_9</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>DCS</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>2</v>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>normal_by_triage</t>
-        </is>
-      </c>
-      <c r="H40" t="n">
-        <v>93.90000000000001</v>
-      </c>
-      <c r="I40" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="J40" t="n">
-        <v>180</v>
-      </c>
-      <c r="K40" t="n">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>U040</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>r2_10</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>DCS</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>2</v>
-      </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>normal_by_triage</t>
-        </is>
-      </c>
-      <c r="H41" t="n">
-        <v>93.90000000000001</v>
-      </c>
-      <c r="I41" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="J41" t="n">
-        <v>180</v>
-      </c>
-      <c r="K41" t="n">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>U041</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>r2_11</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>DCS</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>2</v>
-      </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>normal_by_triage</t>
-        </is>
-      </c>
-      <c r="H42" t="n">
-        <v>93.90000000000001</v>
-      </c>
-      <c r="I42" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="J42" t="n">
-        <v>180</v>
-      </c>
-      <c r="K42" t="n">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>U042</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>r2_12</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>DCS</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>2</v>
-      </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>normal_by_triage</t>
-        </is>
-      </c>
-      <c r="H43" t="n">
-        <v>93.90000000000001</v>
-      </c>
-      <c r="I43" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="J43" t="n">
-        <v>180</v>
-      </c>
-      <c r="K43" t="n">
+      <c r="K28" t="n">
         <v>83</v>
       </c>
     </row>
